--- a/data-source/ESTOQUEPARAGUAI.xlsx
+++ b/data-source/ESTOQUEPARAGUAI.xlsx
@@ -154,10 +154,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data-source/ESTOQUEPARAGUAI.xlsx
+++ b/data-source/ESTOQUEPARAGUAI.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{EB3E627F-C983-4B18-AD05-2EA6762DAB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73EBB94A-344A-4CF6-BAFF-811B61FB52E8}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{EB3E627F-C983-4B18-AD05-2EA6762DAB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{495742EE-33D7-4412-B59B-C37A330B2A6B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A9832E4A-FA62-42FB-B6CE-C34852AF63FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$16</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="14">
   <si>
     <t>Grupo</t>
   </si>
@@ -63,9 +66,6 @@
   </si>
   <si>
     <t>Base Supreme Chassi Bege 435  0.9 mm</t>
-  </si>
-  <si>
-    <t>Base Supreme Chassi White 0.9 mm</t>
   </si>
   <si>
     <t>NEW BASE FLEX 0.95 BISCOITO</t>
@@ -105,7 +105,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -115,6 +115,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -131,14 +137,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -154,6 +162,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -473,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49A2A05-34EC-46FF-A8CE-F1A40FBF4881}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
@@ -501,274 +513,274 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>9073</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2">
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="6">
         <v>780</v>
       </c>
-      <c r="D2">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="6">
+        <v>13</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>6520</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="6">
         <v>16154</v>
       </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="6">
+        <v>13</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>6518</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="4">
+        <v>9073</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6">
+        <v>24584</v>
+      </c>
+      <c r="D4" s="6">
+        <v>13</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>9073</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6">
+        <v>3960</v>
+      </c>
+      <c r="D5" s="6">
+        <v>13</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>9073</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6">
+        <v>16000</v>
+      </c>
+      <c r="D6" s="6">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>9073</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6">
+        <v>30795</v>
+      </c>
+      <c r="D7" s="6">
+        <v>13</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>10608</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4">
-        <v>2842</v>
-      </c>
-      <c r="D4">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="C8" s="6">
+        <v>11279</v>
+      </c>
+      <c r="D8" s="6">
+        <v>13</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>9004</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6">
+        <v>10303</v>
+      </c>
+      <c r="D9" s="6">
+        <v>13</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>9299</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4948</v>
+      </c>
+      <c r="D10" s="6">
+        <v>13</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
         <v>9073</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>24584</v>
-      </c>
-      <c r="D5">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>9073</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>3960</v>
-      </c>
-      <c r="D6">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>9073</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>16000</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="B11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="6">
+        <v>14902</v>
+      </c>
+      <c r="D11" s="6">
+        <v>13</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>9010</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="6">
+        <v>30798</v>
+      </c>
+      <c r="D12" s="6">
+        <v>13</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>9011</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>20915</v>
+      </c>
+      <c r="D13" s="6">
+        <v>13</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
         <v>15721</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8">
-        <v>8200</v>
-      </c>
-      <c r="D8">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>9010</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>3243</v>
-      </c>
-      <c r="D9">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>9073</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10">
-        <v>30795</v>
-      </c>
-      <c r="D10">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>10608</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11">
-        <v>11279</v>
-      </c>
-      <c r="D11">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>9004</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="B14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="6">
+        <v>27180</v>
+      </c>
+      <c r="D14" s="6">
+        <v>13</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>15721</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="6">
+        <v>30610</v>
+      </c>
+      <c r="D15" s="6">
+        <v>13</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>9011</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C12">
-        <v>10303</v>
-      </c>
-      <c r="D12">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>9299</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>4948</v>
-      </c>
-      <c r="D13">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>9073</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14">
-        <v>14902</v>
-      </c>
-      <c r="D14">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>9010</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15">
-        <v>30780</v>
-      </c>
-      <c r="D15">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>9011</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16">
-        <v>30913</v>
-      </c>
-      <c r="D16">
-        <v>13</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="C16" s="6">
+        <v>1040</v>
+      </c>
+      <c r="D16" s="6">
+        <v>13</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="A17" s="4">
         <v>15721</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17">
-        <v>30780</v>
-      </c>
-      <c r="D17">
-        <v>13</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="B17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="6">
+        <v>315</v>
+      </c>
+      <c r="D17" s="6">
+        <v>13</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -785,30 +797,30 @@
       <c r="B21" s="1"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
       <c r="B22" s="1"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
       <c r="B23" s="1"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B24" s="1"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
       <c r="B25" s="1"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
       <c r="B26" s="1"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
       <c r="B27" s="1"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B28" s="1"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
       <c r="B29" s="1"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -818,22 +830,11 @@
       <c r="B31" s="1"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B33" s="1"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B34" s="1"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B35" s="1"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="3"/>
-      <c r="B36" s="1"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:E16" xr:uid="{E49A2A05-34EC-46FF-A8CE-F1A40FBF4881}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data-source/ESTOQUEPARAGUAI.xlsx
+++ b/data-source/ESTOQUEPARAGUAI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{EB3E627F-C983-4B18-AD05-2EA6762DAB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{495742EE-33D7-4412-B59B-C37A330B2A6B}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{EB3E627F-C983-4B18-AD05-2EA6762DAB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D76BFB6F-55DB-460B-B2B6-C345C4EB9C56}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A9832E4A-FA62-42FB-B6CE-C34852AF63FE}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="14">
   <si>
     <t>Grupo</t>
   </si>
@@ -105,7 +105,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -124,6 +124,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -137,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -147,6 +165,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -162,10 +189,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49A2A05-34EC-46FF-A8CE-F1A40FBF4881}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
@@ -514,81 +537,81 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
+        <v>6520</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6">
+        <v>16154</v>
+      </c>
+      <c r="D2" s="6">
+        <v>13</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7">
         <v>9073</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="6">
-        <v>780</v>
-      </c>
-      <c r="D2" s="6">
-        <v>13</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
-        <v>6520</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="6">
-        <v>16154</v>
-      </c>
-      <c r="D3" s="6">
-        <v>13</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>6</v>
+      <c r="C3" s="9">
+        <v>24584</v>
+      </c>
+      <c r="D3" s="9">
+        <v>13</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="A4" s="7">
         <v>9073</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6">
-        <v>24584</v>
-      </c>
-      <c r="D4" s="6">
-        <v>13</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="C4" s="9">
+        <v>16120</v>
+      </c>
+      <c r="D4" s="9">
+        <v>13</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="7">
         <v>9073</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6">
-        <v>3960</v>
-      </c>
-      <c r="D5" s="6">
-        <v>13</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="C5" s="9">
+        <v>30795</v>
+      </c>
+      <c r="D5" s="9">
+        <v>13</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
-        <v>9073</v>
+        <v>10608</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C6" s="6">
-        <v>16000</v>
+        <v>11279</v>
       </c>
       <c r="D6" s="6">
         <v>13</v>
@@ -599,13 +622,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
-        <v>9073</v>
+        <v>9004</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6">
-        <v>30795</v>
+        <v>10303</v>
       </c>
       <c r="D7" s="6">
         <v>13</v>
@@ -616,13 +639,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
-        <v>10608</v>
+        <v>9299</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>11279</v>
+        <v>4948</v>
       </c>
       <c r="D8" s="6">
         <v>13</v>
@@ -632,209 +655,175 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>9004</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="6">
-        <v>10303</v>
-      </c>
-      <c r="D9" s="6">
-        <v>13</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="A9" s="7">
+        <v>9073</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="9">
+        <v>9505</v>
+      </c>
+      <c r="D9" s="9">
+        <v>13</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
-        <v>9299</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>4948</v>
-      </c>
-      <c r="D10" s="6">
-        <v>13</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="A10" s="10">
+        <v>9010</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="12">
+        <v>30798</v>
+      </c>
+      <c r="D10" s="12">
+        <v>13</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
-        <v>9073</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="6">
-        <v>14902</v>
-      </c>
-      <c r="D11" s="6">
-        <v>13</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="A11" s="10">
+        <v>9011</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="12">
+        <v>21315</v>
+      </c>
+      <c r="D11" s="12">
+        <v>13</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
-        <v>9010</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="13">
+        <v>15721</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="15">
+        <v>26980</v>
+      </c>
+      <c r="D12" s="15">
+        <v>13</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>15721</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="15">
+        <v>30610</v>
+      </c>
+      <c r="D13" s="15">
+        <v>13</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
+        <v>9011</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="6">
-        <v>30798</v>
-      </c>
-      <c r="D12" s="6">
-        <v>13</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
-        <v>9011</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6">
-        <v>20915</v>
-      </c>
-      <c r="D13" s="6">
-        <v>13</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="C14" s="12">
+        <v>1040</v>
+      </c>
+      <c r="D14" s="12">
+        <v>13</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
         <v>15721</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="6">
-        <v>27180</v>
-      </c>
-      <c r="D14" s="6">
-        <v>13</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>15721</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="6">
-        <v>30610</v>
-      </c>
-      <c r="D15" s="6">
-        <v>13</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="B15" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="15">
+        <v>315</v>
+      </c>
+      <c r="D15" s="15">
+        <v>13</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>9011</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1040</v>
-      </c>
-      <c r="D16" s="6">
-        <v>13</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>15721</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="6">
-        <v>315</v>
-      </c>
-      <c r="D17" s="6">
-        <v>13</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="1"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E16" xr:uid="{E49A2A05-34EC-46FF-A8CE-F1A40FBF4881}"/>
+  <autoFilter ref="A1:E14" xr:uid="{E49A2A05-34EC-46FF-A8CE-F1A40FBF4881}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data-source/ESTOQUEPARAGUAI.xlsx
+++ b/data-source/ESTOQUEPARAGUAI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{EB3E627F-C983-4B18-AD05-2EA6762DAB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D76BFB6F-55DB-460B-B2B6-C345C4EB9C56}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{EB3E627F-C983-4B18-AD05-2EA6762DAB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{221C9262-3010-4029-9CE9-F4A601BCFD57}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A9832E4A-FA62-42FB-B6CE-C34852AF63FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="14">
   <si>
     <t>Grupo</t>
   </si>
@@ -105,7 +105,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +142,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -155,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -174,6 +180,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49A2A05-34EC-46FF-A8CE-F1A40FBF4881}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
@@ -559,7 +566,7 @@
       <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="16">
         <v>24584</v>
       </c>
       <c r="D3" s="9">
@@ -576,7 +583,7 @@
       <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="16">
         <v>16120</v>
       </c>
       <c r="D4" s="9">
@@ -593,7 +600,7 @@
       <c r="B5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="16">
         <v>30795</v>
       </c>
       <c r="D5" s="9">
@@ -610,7 +617,7 @@
       <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="16">
         <v>11279</v>
       </c>
       <c r="D6" s="6">
@@ -628,7 +635,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="6">
-        <v>10303</v>
+        <v>0</v>
       </c>
       <c r="D7" s="6">
         <v>13</v>
@@ -644,7 +651,7 @@
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="16">
         <v>4948</v>
       </c>
       <c r="D8" s="6">
@@ -661,7 +668,7 @@
       <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="16">
         <v>9505</v>
       </c>
       <c r="D9" s="9">
@@ -678,7 +685,7 @@
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="16">
         <v>30798</v>
       </c>
       <c r="D10" s="12">
@@ -695,8 +702,8 @@
       <c r="B11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="12">
-        <v>21315</v>
+      <c r="C11" s="16">
+        <v>12915</v>
       </c>
       <c r="D11" s="12">
         <v>13</v>
@@ -712,8 +719,8 @@
       <c r="B12" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="15">
-        <v>26980</v>
+      <c r="C12" s="16">
+        <v>23380</v>
       </c>
       <c r="D12" s="15">
         <v>13</v>
@@ -729,7 +736,7 @@
       <c r="B13" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="16">
         <v>30610</v>
       </c>
       <c r="D13" s="15">
@@ -746,8 +753,8 @@
       <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="12">
-        <v>1040</v>
+      <c r="C14" s="16">
+        <v>400</v>
       </c>
       <c r="D14" s="12">
         <v>13</v>
@@ -757,21 +764,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
-        <v>15721</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="15">
-        <v>315</v>
-      </c>
-      <c r="D15" s="15">
-        <v>13</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>5</v>
-      </c>
+      <c r="B15" s="1"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
@@ -783,6 +776,7 @@
       <c r="B18" s="1"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
       <c r="B19" s="1"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -790,14 +784,13 @@
       <c r="B20" s="1"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
       <c r="B21" s="1"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
       <c r="B22" s="1"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
       <c r="B23" s="1"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -816,11 +809,8 @@
       <c r="B28" s="1"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
       <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E14" xr:uid="{E49A2A05-34EC-46FF-A8CE-F1A40FBF4881}"/>
